--- a/astro-site/public/dl/pack-appcc/BONUS-02-protocolo-alerta-alimentaria.xlsx
+++ b/astro-site/public/dl/pack-appcc/BONUS-02-protocolo-alerta-alimentaria.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Protocolo Alerta" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protocolo Alerta" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -108,7 +108,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -130,35 +130,69 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -518,15 +552,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -534,6 +569,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -541,9 +577,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -565,13 +599,19 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -579,7 +619,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -588,16 +637,17 @@
   <sheetPr>
     <tabColor rgb="00FF4444"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:C36"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="60"/>
-    <col customWidth="1" max="3" min="3" width="35"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="4" t="inlineStr">
         <is>
@@ -612,13 +662,14 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="6" t="inlineStr">
         <is>
           <t>PASO 1: IDENTIFICAR</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n"/>
+      <c r="C5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="8" t="inlineStr">
@@ -632,13 +683,14 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
         <is>
           <t>PASO 2: AISLAR</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n"/>
+      <c r="C8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="8" t="inlineStr">
@@ -652,13 +704,14 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
           <t>PASO 3: NOTIFICAR</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n"/>
+      <c r="C11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
@@ -672,13 +725,14 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
           <t>PASO 4: DOCUMENTAR</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n"/>
+      <c r="C14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
@@ -692,13 +746,14 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
           <t>PASO 5: COMUNICAR</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n"/>
+      <c r="C17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="8" t="inlineStr">
@@ -712,13 +767,14 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
           <t>PASO 6: VERIFICAR</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
+      <c r="C20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="8" t="inlineStr">
@@ -732,13 +788,14 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
           <t>PASO 7: REGISTRAR</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
+      <c r="C23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="8" t="inlineStr">
@@ -752,13 +809,15 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="B27" s="10" t="inlineStr">
         <is>
           <t>TELÉFONOS DE EMERGENCIA</t>
         </is>
       </c>
-      <c r="C27" s="11" t="n"/>
+      <c r="C27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="12" t="inlineStr">
@@ -820,6 +879,8 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
@@ -838,15 +899,23 @@
   <mergeCells count="9">
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B14:C14"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/BONUS-02-protocolo-alerta-alimentaria.xlsx
+++ b/astro-site/public/dl/pack-appcc/BONUS-02-protocolo-alerta-alimentaria.xlsx
@@ -10,7 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protocolo Alerta" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Protocolo Alerta'!$A$1:$C$38</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,8 +84,37 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -107,8 +139,18 @@
         <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -163,11 +205,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -188,6 +244,38 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -554,24 +642,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>BONUS: Protocolo de Actuación ante Alerta Alimentaria</t>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>BONUS — Protocolo de Actuación ante Alerta Alimentaria</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla</t>
         </is>
@@ -579,47 +667,127 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ Imprime en tamaño A3 y coloca en zona visible de cocina</t>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>▸ Rellena los teléfonos de la tabla de contactos ANTES de necesitarlos, empezando por el de Salud Pública de tu comunidad autónoma.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ Todo el personal debe conocer estos pasos</t>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>▸ Imprime el cartel en A4 (o amplíalo a A3 desde el diálogo de impresión) y cuélgalo en zona visible de cocina.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ Actuar rápido puede evitar sanciones y proteger al cliente</t>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>▸ Repasa los siete pasos con todo el equipo y déjalo anotado en el registro de formación (BONUS-01).</t>
         </is>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Lo que cambia respecto de lo que suele hacerse</t>
         </is>
       </c>
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Ante la sospecha de un alimento nocivo, la obligación legal no es llamar al 112: es notificar de inmediato a la autoridad sanitaria de tu comunidad autónoma y retirar el producto (art. 19 del Reg. (CE) 178/2002). Esa autoridad es la que activa la red de alerta SCIRI a través de AESAN. El 112 se llama solo si hay una persona con síntomas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Cuándo se activa este protocolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>▸ Recibes una notificación de retirada de tu proveedor o de la autoridad sanitaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>▸ Detectas un producto en mal estado que ya se ha usado o servido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>▸ Un cliente comunica un malestar que puede relacionarse con algo que has servido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>▸ Se rompe la cadena de frío de un lote que ya se ha distribuido o servido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Con qué registros se enlaza</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>▸ Registro 06 (trazabilidad): para saber de dónde vino el lote y a qué elaboraciones y servicios fue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>▸ Registro 11 (acciones correctivas): ahí se documenta la incidencia y el destino del producto no conforme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>▸ Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2"/>
-  </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
@@ -639,275 +807,305 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>PROTOCOLO DE ACTUACIÓN ANTE ALERTA ALIMENTARIA</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Seguir estos pasos en orden. No improvisar.</t>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Seguir estos pasos EN ORDEN. No improvisar. Colgar este cartel en zona visible de cocina.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>PASO 1: IDENTIFICAR</t>
         </is>
       </c>
       <c r="C5" s="15" t="n"/>
     </row>
-    <row r="6">
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Identificar el producto afectado (nombre, lote, proveedor, fecha recepción)</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Consultar registro de trazabilidad</t>
+    <row r="6" ht="30" customHeight="1">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Identificar el producto afectado: nombre, nº de lote, proveedor y fecha de recepción.</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Consultar el registro 06 de trazabilidad (entrada y salida).</t>
         </is>
       </c>
     </row>
     <row r="7"/>
-    <row r="8">
-      <c r="B8" s="6" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>PASO 2: AISLAR</t>
         </is>
       </c>
       <c r="C8" s="15" t="n"/>
     </row>
-    <row r="9">
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Retirar INMEDIATAMENTE el producto de la cadena alimentaria</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Marcar como 'NO USAR — ALERTA' y separar en zona aislada</t>
+    <row r="9" ht="39" customHeight="1">
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Retirar INMEDIATAMENTE el producto de la cadena alimentaria. No servirlo, no cocinarlo, no devolverlo al almacén general.</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Marcar «NO USAR — ALERTA» y separarlo en una zona aislada e identificada.</t>
         </is>
       </c>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>PASO 3: NOTIFICAR</t>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>PASO 3: NOTIFICAR A LA AUTORIDAD SANITARIA</t>
         </is>
       </c>
       <c r="C11" s="15" t="n"/>
     </row>
-    <row r="12">
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Avisar al responsable de calidad / gerente del establecimiento</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Si hay riesgo para la salud: llamar al 112 / Sanidad</t>
+    <row r="12" ht="91" customHeight="1">
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Notificar de inmediato a la autoridad sanitaria de tu comunidad autónoma (Salud Pública) y al proveedor. Es una OBLIGACIÓN LEGAL del art. 19 del Reg. (CE) 178/2002 cuando se sospecha que un alimento puesto en el mercado puede ser nocivo; la autoridad es quien activa la red de alerta (SCIRI / AESAN).</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>El 112 SOLO si hay una persona con síntomas: es emergencia médica, no el cauce de notificación de una alerta. Avisar también al responsable de calidad o al gerente.</t>
         </is>
       </c>
     </row>
     <row r="13"/>
-    <row r="14">
-      <c r="B14" s="6" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>PASO 4: DOCUMENTAR</t>
         </is>
       </c>
       <c r="C14" s="15" t="n"/>
     </row>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Registrar: qué producto, cuánto hay en stock, a quién se ha servido</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Completar hoja de Acciones Correctivas</t>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Registrar qué producto es, cuánto queda en stock, cuánto se ha servido y a quién.</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Completar el registro 11 de Acciones Correctivas con el nº de incidencia.</t>
         </is>
       </c>
     </row>
     <row r="16"/>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>PASO 5: COMUNICAR</t>
         </is>
       </c>
       <c r="C17" s="15" t="n"/>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Si se ha servido al público: evaluar si hay que informar a los clientes</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Contactar con el proveedor para coordinar retirada</t>
+    <row r="18" ht="52" customHeight="1">
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Si el producto se ha servido al público, informar a los clientes afectados que se puedan identificar y seguir las instrucciones de la autoridad sanitaria.</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Coordinar con el proveedor la retirada y la devolución del producto.</t>
         </is>
       </c>
     </row>
     <row r="19"/>
-    <row r="20">
-      <c r="B20" s="6" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>PASO 6: VERIFICAR</t>
         </is>
       </c>
       <c r="C20" s="15" t="n"/>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Comprobar que no queda producto afectado en ningún punto del local</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Revisar cámaras, almacén, sala, preparaciones en curso</t>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Comprobar que no queda producto afectado en ningún punto del local.</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>Revisar cámaras, congeladores, almacén, sala, mise en place y elaboraciones en curso.</t>
         </is>
       </c>
     </row>
     <row r="22"/>
-    <row r="23">
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>PASO 7: REGISTRAR</t>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>PASO 7: REGISTRAR Y REVISAR</t>
         </is>
       </c>
       <c r="C23" s="15" t="n"/>
     </row>
-    <row r="24">
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Documentar todo el proceso: fechas, acciones, personas implicadas</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Archivar junto con el registro de acciones correctivas</t>
+    <row r="24" ht="39" customHeight="1">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Documentar todo el proceso: fechas, horas, acciones, personas implicadas y desenlace.</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Archivar con el registro 11 y revisar si hay que cambiar algún procedimiento para que no se repita.</t>
         </is>
       </c>
     </row>
     <row r="25"/>
     <row r="26"/>
     <row r="27">
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>TELÉFONOS DE EMERGENCIA</t>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>TELÉFONOS Y CONTACTOS</t>
         </is>
       </c>
       <c r="C27" s="15" t="n"/>
     </row>
-    <row r="28">
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>Emergencias generales</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Salud Pública / Autoridad sanitaria de tu comunidad autónoma</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>(completar — es la notificación obligatoria del art. 19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>Emergencias médicas (solo si hay personas con síntomas)</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Centro de Salud más cercano</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>Centro de salud más cercano</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>(completar)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Responsable de calidad</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>Responsable de calidad del establecimiento</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
         <is>
           <t>(nombre + teléfono)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>Empresa control de plagas</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
+    <row r="32" ht="24" customHeight="1">
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>Proveedor del producto afectado</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
         <is>
           <t>(nombre + teléfono)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>Proveedor principal</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
+    <row r="33" ht="24" customHeight="1">
+      <c r="B33" s="26" t="inlineStr">
+        <is>
+          <t>Empresa de control de plagas</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
         <is>
           <t>(nombre + teléfono)</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34"/>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Imprimir en A3 y colocar en zona visible. Todo el personal debe conocer este protocolo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+    <row r="35" ht="24.5" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>Base legal: art. 19 del Reg. (CE) 178/2002 — si sospechas que un alimento que has puesto en el mercado puede ser nocivo, tienes que retirarlo e informar de inmediato a la autoridad competente. El 112 es emergencia médica y no sustituye a esa notificación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24.5" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>Imprime este cartel en A4 (o amplíalo a A3 desde el diálogo de impresión de tu equipo) y cuélgalo en zona visible de cocina. Todo el personal debe conocerlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24.5" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="12.2" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="14">
+    <mergeCell ref="A38:C38"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A36:C36"/>
     <mergeCell ref="B14:C14"/>
   </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>

--- a/astro-site/public/dl/pack-appcc/BONUS-02-protocolo-alerta-alimentaria.xlsx
+++ b/astro-site/public/dl/pack-appcc/BONUS-02-protocolo-alerta-alimentaria.xlsx
@@ -1090,20 +1090,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="A38:C38"/>
-    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B27:C27"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A36:C36"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
